--- a/data/trans_dic/P37A$vacunaempresa-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P37A$vacunaempresa-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,04</t>
+          <t>0,8; 2,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,25; 6,35</t>
+          <t>2,41; 6,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,0</t>
+          <t>0,46; 3,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,94; 8,21</t>
+          <t>4,18; 8,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,98</t>
+          <t>0,64; 4,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,27; 5,57</t>
+          <t>1,5; 5,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 4,07</t>
+          <t>1,08; 4,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,86; 10,64</t>
+          <t>5,54; 10,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 2,91</t>
+          <t>0,99; 2,8</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,23; 5,17</t>
+          <t>2,3; 5,12</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,99</t>
+          <t>0,97; 2,91</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,48; 8,64</t>
+          <t>5,41; 8,25</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -857,32 +857,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,82; 6,56</t>
+          <t>1,78; 6,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,93; 6,34</t>
+          <t>1,87; 6,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,39</t>
+          <t>0,27; 2,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,83; 8,21</t>
+          <t>3,77; 8,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,11</t>
+          <t>0,0; 1,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,91</t>
+          <t>0,34; 3,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -892,27 +892,27 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,34; 5,5</t>
+          <t>2,19; 5,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,4</t>
+          <t>1,09; 3,4</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,38; 4,19</t>
+          <t>1,42; 4,14</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,4</t>
+          <t>0,25; 1,42</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,6; 6,55</t>
+          <t>3,58; 6,39</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -997,22 +997,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,37</t>
+          <t>0,15; 1,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,05</t>
+          <t>0,0; 0,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,08</t>
+          <t>0,0; 0,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,51</t>
+          <t>0,7; 3,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1032,12 +1032,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,43</t>
+          <t>0,0; 2,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,06</t>
+          <t>0,11; 1,17</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1047,12 +1047,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,83</t>
+          <t>0,0; 0,82</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,92</t>
+          <t>0,61; 2,4</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,42</t>
+          <t>0,45; 1,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1147,52 +1147,52 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,79</t>
+          <t>0,09; 0,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,54</t>
+          <t>0,89; 2,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,85</t>
+          <t>0,31; 1,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,12</t>
+          <t>0,91; 3,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,34</t>
+          <t>0,59; 2,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,62; 6,95</t>
+          <t>4,5; 7,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,36</t>
+          <t>0,5; 1,34</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,59</t>
+          <t>0,6; 1,65</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,16</t>
+          <t>0,36; 1,2</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,09; 4,1</t>
+          <t>2,63; 4,15</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -1277,32 +1277,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,37</t>
+          <t>0,0; 1,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,03</t>
+          <t>0,36; 2,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,43</t>
+          <t>0,0; 1,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,12</t>
+          <t>0,26; 2,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,37</t>
+          <t>0,16; 1,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,22</t>
+          <t>0,12; 1,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1312,34 +1312,34 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,73</t>
+          <t>0,65; 1,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,95</t>
+          <t>0,1; 1,03</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,27</t>
+          <t>0,3; 1,19</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,69</t>
+          <t>0,0; 0,65</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,48</t>
+          <t>0,61; 1,55</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,0</t>
+          <t>0,0; 2,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,23</t>
+          <t>0,0; 6,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1452,17 +1452,17 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,06; 1,19</t>
+          <t>0,07; 1,24</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,33</t>
+          <t>0,0; 0,29</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,52</t>
+          <t>0,0; 0,54</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,24</t>
+          <t>0,21; 1,62</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,52</t>
+          <t>0,76; 1,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,99; 1,87</t>
+          <t>0,99; 1,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,76</t>
+          <t>0,25; 0,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,0; 3,32</t>
+          <t>2,22; 3,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,83</t>
+          <t>0,33; 0,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,6; 1,28</t>
+          <t>0,54; 1,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,83</t>
+          <t>0,31; 0,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,44; 3,71</t>
+          <t>2,69; 3,7</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,6; 1,02</t>
+          <t>0,61; 1,06</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,85; 1,4</t>
+          <t>0,86; 1,4</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,72</t>
+          <t>0,36; 0,71</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,38; 3,35</t>
+          <t>2,57; 3,4</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30343</t>
+          <t>32414</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>36002</t>
+          <t>36792</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>66345</t>
+          <t>69206</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3626; 14419</t>
+          <t>3790; 14132</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9844; 27749</t>
+          <t>10552; 28217</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2034; 12852</t>
+          <t>1952; 13348</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19920; 41473</t>
+          <t>22993; 45540</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1966; 12197</t>
+          <t>1966; 12643</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3985; 17505</t>
+          <t>4710; 17530</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3575; 14142</t>
+          <t>3763; 15145</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>26217; 47599</t>
+          <t>27066; 49359</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7969; 22710</t>
+          <t>7745; 21880</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16749; 38848</t>
+          <t>17295; 38451</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7639; 23241</t>
+          <t>7541; 22588</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>52199; 82333</t>
+          <t>56186; 85697</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26906</t>
+          <t>28494</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13773</t>
+          <t>14480</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>40680</t>
+          <t>42974</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6686; 24071</t>
+          <t>6534; 22587</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8092; 26571</t>
+          <t>7833; 26209</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1019; 9018</t>
+          <t>1010; 9909</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17326; 37120</t>
+          <t>18196; 40658</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 7864</t>
+          <t>0; 6711</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1105; 13203</t>
+          <t>1134; 12996</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4458</t>
+          <t>0; 4479</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8969; 21025</t>
+          <t>9278; 22686</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7608; 25091</t>
+          <t>8060; 25149</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10447; 31721</t>
+          <t>10725; 31323</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1854; 10509</t>
+          <t>1866; 10617</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>30028; 54670</t>
+          <t>32427; 57961</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6937</t>
+          <t>7227</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8242</t>
+          <t>8670</t>
         </is>
       </c>
     </row>
@@ -2343,22 +2343,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>816; 7447</t>
+          <t>803; 8058</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 6594</t>
+          <t>0; 5858</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5659</t>
+          <t>0; 4828</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1552; 16804</t>
+          <t>3305; 15113</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2378,27 +2378,27 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4063</t>
+          <t>0; 4817</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>814; 7537</t>
+          <t>813; 8323</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 6611</t>
+          <t>0; 6587</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 5701</t>
+          <t>0; 5609</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1843; 16042</t>
+          <t>4001; 15802</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16197</t>
+          <t>16849</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>48223</t>
+          <t>49306</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>64420</t>
+          <t>66155</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5224; 17538</t>
+          <t>5632; 18746</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2132; 14089</t>
+          <t>2075; 14137</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>989; 9073</t>
+          <t>989; 8159</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8600; 26264</t>
+          <t>10048; 28924</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2851; 13242</t>
+          <t>2236; 13239</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6840; 23925</t>
+          <t>6939; 23995</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5168; 19315</t>
+          <t>4857; 19169</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25673; 68017</t>
+          <t>38794; 64020</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10006; 26587</t>
+          <t>9849; 26096</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11032; 30572</t>
+          <t>11641; 31817</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7436; 22873</t>
+          <t>7126; 23658</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>42057; 82588</t>
+          <t>52395; 82790</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>4984</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>9030</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11989</t>
+          <t>14014</t>
         </is>
       </c>
     </row>
@@ -2759,32 +2759,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4815</t>
+          <t>0; 5079</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1847; 10345</t>
+          <t>1833; 10440</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 8858</t>
+          <t>0; 10200</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1016; 10074</t>
+          <t>1485; 11669</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>918; 7810</t>
+          <t>918; 8729</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>961; 9255</t>
+          <t>945; 10100</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2794,34 +2794,34 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4590; 14582</t>
+          <t>5370; 14487</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>928; 8742</t>
+          <t>928; 9513</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4626; 16142</t>
+          <t>3843; 15120</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 9407</t>
+          <t>0; 8843</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7231; 19534</t>
+          <t>8563; 21738</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>4103</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>3091</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>8327</t>
+          <t>7354</t>
         </is>
       </c>
     </row>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5327</t>
+          <t>0; 6594</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2982,12 +2982,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 17389</t>
+          <t>0; 15623</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 5835</t>
+          <t>0; 5836</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -3002,17 +3002,17 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>476; 9041</t>
+          <t>551; 10462</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 5120</t>
+          <t>0; 4494</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 7166</t>
+          <t>0; 7466</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2568; 22412</t>
+          <t>2225; 17573</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>89399</t>
+          <t>94072</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>110604</t>
+          <t>114301</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>200003</t>
+          <t>208373</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>25138; 49833</t>
+          <t>24915; 48056</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>33979; 63999</t>
+          <t>33941; 64467</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8899; 25777</t>
+          <t>8337; 26413</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>67438; 111927</t>
+          <t>76262; 115361</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>10984; 28010</t>
+          <t>11083; 27504</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21252; 45333</t>
+          <t>19321; 43212</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11197; 29423</t>
+          <t>10969; 29261</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>87360; 132707</t>
+          <t>97662; 134677</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>40169; 67491</t>
+          <t>40305; 70267</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>59482; 97385</t>
+          <t>60057; 97276</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23659; 49770</t>
+          <t>24962; 48941</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>165673; 232721</t>
+          <t>182011; 240377</t>
         </is>
       </c>
     </row>
